--- a/Base_Template/template_mt_parceiros.xlsx
+++ b/Base_Template/template_mt_parceiros.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="204">
   <si>
     <t>PORTAL MT PARCEIROS</t>
   </si>
@@ -371,7 +371,7 @@
     <t>💬 Iniciar Atendimento</t>
   </si>
   <si>
-    <t>🤖 Simulação gerada por Algoritmo de IA MT Parceiros  •  Gerado em 02/03/2026 • © MT Parceiros</t>
+    <t>🤖 Simulação gerada por Algoritmo de IA MT Parceiros  •  Gerado em 03/03/2026 • © MT Parceiros</t>
   </si>
   <si>
     <t>📊 ANÁLISE EXECUTIVA (Algoritmo IA)</t>
@@ -392,9 +392,6 @@
     <t xml:space="preserve">  CRÉDITO CAIXA MAX</t>
   </si>
   <si>
-    <t xml:space="preserve">  SUBSÍDIO ESTIMADO</t>
-  </si>
-  <si>
     <t xml:space="preserve">  SALDO FGTS</t>
   </si>
   <si>
@@ -407,6 +404,21 @@
     <t xml:space="preserve">  HISTÓRICO CARTEIRA</t>
   </si>
   <si>
+    <t>📋 ENQUADRAMENTO E SUBSÍDIOS</t>
+  </si>
+  <si>
+    <t>FAIXA MCMV</t>
+  </si>
+  <si>
+    <t>SUBSÍDIO FEDERAL</t>
+  </si>
+  <si>
+    <t>CASA PAULISTA (SP)</t>
+  </si>
+  <si>
+    <t>TOTAL SUBSÍDIOS</t>
+  </si>
+  <si>
     <t>SEU SCORE MT PARCEIROS</t>
   </si>
   <si>
@@ -497,7 +509,10 @@
     <t>Seu Crédito CAIXA (Max):</t>
   </si>
   <si>
-    <t>Subsídio MCMV Estimado:</t>
+    <t>Subsídio Federal (MCMV):</t>
+  </si>
+  <si>
+    <t>Subsídio Estadual (Casa Paulista):</t>
   </si>
   <si>
     <t>PODER DE COMPRA TOTAL:</t>
@@ -628,7 +643,7 @@
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="mmm/yy"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="41">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -795,15 +810,36 @@
     </font>
     <font>
       <b/>
-      <sz val="36"/>
-      <color rgb="FFF35525"/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Poppins"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
+      <color rgb="FF1A1A2E"/>
+      <name val="Poppins"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF2980B9"/>
+      <name val="Poppins"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF27AE60"/>
+      <name val="Poppins"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="36"/>
+      <color rgb="FFF35525"/>
       <name val="Poppins"/>
       <family val="2"/>
     </font>
@@ -886,7 +922,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -937,6 +973,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF2980B9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF8FAFC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -954,7 +996,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -1179,6 +1221,19 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF2980B9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF2980B9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF2980B9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFE2E8F0"/>
       </left>
       <right style="thin">
@@ -1196,7 +1251,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1284,43 +1339,67 @@
     <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -1328,22 +1407,22 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="35" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1353,22 +1432,22 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="36" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="39" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2447,7 +2526,7 @@
       <c r="D14" s="31"/>
       <c r="F14" s="30"/>
       <c r="G14" s="31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H14" s="31"/>
     </row>
@@ -2473,7 +2552,7 @@
       <c r="D18" s="31"/>
       <c r="F18" s="30"/>
       <c r="G18" s="31" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H18" s="31"/>
     </row>
@@ -2499,14 +2578,14 @@
       <c r="D22" s="31"/>
       <c r="F22" s="30"/>
       <c r="G22" s="31" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H22" s="31"/>
     </row>
     <row r="23" spans="2:12" ht="30" customHeight="1">
       <c r="B23" s="30"/>
       <c r="C23" s="32">
-        <f>'Educação Financeira'!$E30</f>
+        <f>'Educação Financeira'!$E24</f>
         <v>0</v>
       </c>
       <c r="F23" s="30"/>
@@ -2517,113 +2596,147 @@
     </row>
     <row r="24" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="25" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1"/>
-    <row r="26" spans="2:12">
-      <c r="B26" s="30"/>
-      <c r="C26" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="D26" s="31"/>
-    </row>
-    <row r="27" spans="2:12" ht="30" customHeight="1">
-      <c r="B27" s="30"/>
-      <c r="C27" s="32">
-        <f>'Educação Financeira'!$E24</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1"/>
+    <row r="26" spans="2:12" ht="25" customHeight="1">
+      <c r="C26" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
+      <c r="C27" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="D27" s="35"/>
+      <c r="E27" s="36" t="s">
+        <v>129</v>
+      </c>
+      <c r="F27" s="36"/>
+      <c r="G27" s="36"/>
+      <c r="H27" s="37" t="s">
+        <v>130</v>
+      </c>
+      <c r="I27" s="37"/>
+      <c r="J27" s="37"/>
+      <c r="K27" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="L27" s="38"/>
+    </row>
+    <row r="28" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
+      <c r="C28" s="39">
+        <f>IF('Educação Financeira'!E13&lt;=2850, "FAIXA 1", IF('Educação Financeira'!E13&lt;=4700, "FAIXA 2", IF('Educação Financeira'!E13&lt;=8000, "FAIXA 3", "FORA DO MCMV")))</f>
+        <v>0</v>
+      </c>
+      <c r="D28" s="39"/>
+      <c r="E28" s="40">
+        <f>IF('Educação Financeira'!E13&lt;=2850, "R$ 55.000", IF('Educação Financeira'!E13&lt;=4700, "R$ 35.000", "Não se aplica"))</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="40"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="41">
+        <f>IF('Educação Financeira'!E13&lt;=4863, "✅ R$ 16.000", "❌ Não elegível")</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="41"/>
+      <c r="J28" s="41"/>
+      <c r="K28" s="42">
+        <f>IF('Educação Financeira'!E13&lt;=2850, 55000, IF('Educação Financeira'!E13&lt;=4700, 35000, 0)) + IF('Educação Financeira'!E13&lt;=4863, 16000, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="L28" s="42"/>
+    </row>
     <row r="29" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="30" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C30" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
       <c r="G30" s="8" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="C31" s="35">
+      <c r="C31" s="43">
         <f>MIN(100, MIN(40, MAX(0, 40-((('Educação Financeira'!E33/'Educação Financeira'!E13)-0.25)*200))) + MIN(30, 'Educação Financeira'!E24/50000*30) + IF('Educação Financeira'!E26="SIM",30,10))</f>
         <v>0</v>
       </c>
-      <c r="D31" s="35"/>
-      <c r="E31" s="35"/>
-      <c r="G31" s="36" t="s">
-        <v>130</v>
-      </c>
-      <c r="H31" s="36"/>
-      <c r="I31" s="37" t="s">
-        <v>131</v>
-      </c>
-      <c r="J31" s="37"/>
-      <c r="K31" s="37" t="s">
-        <v>132</v>
-      </c>
-      <c r="L31" s="37"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
+      <c r="G31" s="44" t="s">
+        <v>134</v>
+      </c>
+      <c r="H31" s="44"/>
+      <c r="I31" s="45" t="s">
+        <v>135</v>
+      </c>
+      <c r="J31" s="45"/>
+      <c r="K31" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="L31" s="45"/>
     </row>
     <row r="32" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="C32" s="35"/>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="36"/>
-      <c r="I32" s="37"/>
-      <c r="J32" s="37"/>
-      <c r="K32" s="37"/>
-      <c r="L32" s="37"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="43"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="44"/>
+      <c r="I32" s="45"/>
+      <c r="J32" s="45"/>
+      <c r="K32" s="45"/>
+      <c r="L32" s="45"/>
     </row>
     <row r="33" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="34" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="35" spans="2:12" ht="25" customHeight="1">
       <c r="C35" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="36" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="I36" s="38">
+      <c r="I36" s="46">
         <f>IF(IFERROR('Educação Financeira'!E33 / 'Educação Financeira'!E13, 0)&gt;0, REPT("▓", INT(MIN(30, IFERROR('Educação Financeira'!E33 / 'Educação Financeira'!E13, 0) * 100))), "")</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="C37" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="E37" s="40">
+      <c r="C37" s="47" t="s">
+        <v>138</v>
+      </c>
+      <c r="E37" s="48">
         <f>'Educação Financeira'!E29</f>
         <v>0</v>
       </c>
-      <c r="G37" s="41">
+      <c r="G37" s="49">
         <f>IF(E37&gt;0, REPT("█", INT(MIN(20, E37/20000))), "")</f>
         <v>0</v>
       </c>
-      <c r="I37" s="39" t="s">
-        <v>138</v>
+      <c r="I37" s="47" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="38" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="I38" s="39" t="s">
+      <c r="I38" s="47" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
+      <c r="C39" s="47" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="39" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="C39" s="39" t="s">
-        <v>135</v>
-      </c>
-      <c r="E39" s="40">
+      <c r="E39" s="48">
         <f>'Educação Financeira'!E30</f>
         <v>0</v>
       </c>
-      <c r="G39" s="42">
+      <c r="G39" s="50">
         <f>IF(E39&gt;0, REPT("█", INT(MIN(20, E39/5000))), "")</f>
         <v>0</v>
       </c>
-      <c r="I39" s="43">
+      <c r="I39" s="51">
         <f>IF(IFERROR(1 - ('Educação Financeira'!E33 / 'Educação Financeira'!E13), 0)&gt;0, REPT("▓", INT(MIN(30, IFERROR(1 - ('Educação Financeira'!E33 / 'Educação Financeira'!E13), 0) * 100))), "")</f>
         <v>0</v>
       </c>
@@ -2755,7 +2868,7 @@
     <row r="150" s="3" customFormat="1" ht="20" customHeight="1"/>
   </sheetData>
   <sheetProtection sheet="1" autoFilter="0"/>
-  <mergeCells count="28">
+  <mergeCells count="34">
     <mergeCell ref="B1:L1"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="E3:F3"/>
@@ -2770,14 +2883,20 @@
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="B22:B23"/>
     <mergeCell ref="C22:D22"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:D26"/>
     <mergeCell ref="F14:F15"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="F18:F19"/>
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="F22:F23"/>
     <mergeCell ref="G22:H22"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="K28:L28"/>
     <mergeCell ref="C30:E30"/>
     <mergeCell ref="C31:E32"/>
     <mergeCell ref="G31:H32"/>
@@ -2825,7 +2944,7 @@
       <c r="J1" s="25"/>
       <c r="K1" s="25"/>
       <c r="L1" s="25"/>
-      <c r="Z1" s="40">
+      <c r="Z1" s="48">
         <f>E38</f>
         <v>0</v>
       </c>
@@ -2847,7 +2966,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="1"/>
-      <c r="Z3" s="44">
+      <c r="Z3" s="52">
         <f>IFERROR(VLOOKUP(E36, Table_Empreendimentos[[Nome]:[Prazo_Meses]], 10, FALSE), "Pronto")</f>
         <v>0</v>
       </c>
@@ -2866,7 +2985,7 @@
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
-      <c r="Z4" s="44">
+      <c r="Z4" s="52">
         <f>IFERROR(VLOOKUP(E36, Table_Empreendimentos[[Nome]:[Prazo_Meses]], 11, FALSE), 1)</f>
         <v>0</v>
       </c>
@@ -2874,7 +2993,7 @@
     <row r="5" spans="2:26" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="6" spans="2:26" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C6" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
@@ -2887,25 +3006,25 @@
     </row>
     <row r="7" spans="2:26" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C7" s="5" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="2:26" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C8" s="8" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="2:26" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="C9" s="45">
+      <c r="C9" s="53">
         <f>'Início'!E23</f>
         <v>0</v>
       </c>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="53"/>
     </row>
     <row r="10" spans="2:26" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C10" s="27" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D10" s="27"/>
       <c r="E10" s="27"/>
@@ -2929,83 +3048,83 @@
     </row>
     <row r="12" spans="2:26" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C12" s="6" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="2:26" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C13" s="8" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E13" s="18">
         <v>8000</v>
       </c>
-      <c r="G13" s="43">
+      <c r="G13" s="51">
         <f>IF(E13&gt;0, REPT("█", INT(MIN(20, E13/1000))), "")</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:26" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C14" s="8" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E14" s="18">
         <v>15000</v>
       </c>
-      <c r="G14" s="41">
+      <c r="G14" s="49">
         <f>IF(E14&gt;0, REPT("█", INT(MIN(20, E14/2000))), "")</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:26" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C15" s="6" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16" spans="2:26" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="17" spans="3:7" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C17" s="8" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E17" s="18">
         <v>1200</v>
       </c>
-      <c r="G17" s="38">
+      <c r="G17" s="46">
         <f>IF(E17&gt;0, REPT("█", INT(MIN(20, E17/500))), "")</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="3:7" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C18" s="8" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E18" s="18">
         <v>800</v>
       </c>
-      <c r="G18" s="38">
+      <c r="G18" s="46">
         <f>IF(E18&gt;0, REPT("█", INT(MIN(20, E18/500))), "")</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="3:7" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C19" s="8" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E19" s="18">
         <v>400</v>
       </c>
-      <c r="G19" s="38">
+      <c r="G19" s="46">
         <f>IF(E19&gt;0, REPT("█", INT(MIN(20, E19/500))), "")</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="3:7" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C20" s="8" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E20" s="18">
         <v>0</v>
       </c>
-      <c r="G20" s="38">
+      <c r="G20" s="46">
         <f>IF(E20&gt;0, REPT("█", INT(MIN(20, E20/500))), "")</f>
         <v>0</v>
       </c>
@@ -3013,9 +3132,9 @@
     <row r="21" spans="3:7" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="22" spans="3:7" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C22" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="E22" s="46">
+        <v>156</v>
+      </c>
+      <c r="E22" s="54">
         <f>SUM(E17:E21)</f>
         <v>0</v>
       </c>
@@ -3023,12 +3142,12 @@
     <row r="23" spans="3:7" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="24" spans="3:7" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C24" s="8" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E24" s="18">
         <v>30000</v>
       </c>
-      <c r="G24" s="41">
+      <c r="G24" s="49">
         <f>IF(E24&gt;0, REPT("█", INT(MIN(20, E24/2000))), "")</f>
         <v>0</v>
       </c>
@@ -3036,51 +3155,58 @@
     <row r="25" spans="3:7" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="26" spans="3:7" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C26" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="E26" s="47" t="s">
-        <v>155</v>
+        <v>158</v>
+      </c>
+      <c r="E26" s="55" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="27" spans="3:7" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="28" spans="3:7" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C28" s="6" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" spans="3:7" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C29" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="E29" s="40">
+        <v>161</v>
+      </c>
+      <c r="E29" s="48">
         <f>ROUND(MAX(0, (E13*0.30 - E22) * IF(E26="SIM", 142, 132)), 0)</f>
         <v>0</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="30" spans="3:7" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C30" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="E30" s="40">
+        <v>162</v>
+      </c>
+      <c r="E30" s="48">
         <f>IF(E13&lt;=2850, 55000, IF(E13&lt;=4700, 35000, 0))</f>
+        <v>0</v>
+      </c>
+      <c r="G30" s="48">
+        <f>IF(E13&lt;=4863, 16000, 0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="3:7" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C31" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="E31" s="48">
-        <f>E29 + E30 + E24 + E14</f>
+        <v>164</v>
+      </c>
+      <c r="E31" s="56">
+        <f>E29 + E30 + G30 + E24 + E14</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="3:7" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="33" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C33" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="E33" s="40">
+        <v>165</v>
+      </c>
+      <c r="E33" s="48">
         <f>MAX(0, (E13 * 0.30) - E22)</f>
         <v>0</v>
       </c>
@@ -3088,42 +3214,42 @@
     <row r="34" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="35" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C35" s="6" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="36" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C36" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="E36" s="49" t="s">
-        <v>163</v>
-      </c>
-      <c r="F36" s="49"/>
+        <v>167</v>
+      </c>
+      <c r="E36" s="57" t="s">
+        <v>168</v>
+      </c>
+      <c r="F36" s="57"/>
     </row>
     <row r="37" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="38" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C38" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="E38" s="48">
+        <v>169</v>
+      </c>
+      <c r="E38" s="56">
         <f>IFERROR(VLOOKUP(E36, Table_Empreendimentos[[Nome]:[Prazo_Meses]], 2, FALSE), 0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C39" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="E39" s="50">
+        <v>170</v>
+      </c>
+      <c r="E39" s="58">
         <f>IFERROR(VLOOKUP(E36, Table_Empreendimentos[[Nome]:[Prazo_Meses]], 5, FALSE), "---")</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C40" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="E40" s="51">
+        <v>171</v>
+      </c>
+      <c r="E40" s="59">
         <f>HYPERLINK("https://mtparceiros-alt.github.io/site-mt", "🔗 Abrir Imóvel")</f>
         <v>0</v>
       </c>
@@ -3131,66 +3257,66 @@
     <row r="41" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="42" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C42" s="6" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="43" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C43" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="E43" s="40">
+        <v>173</v>
+      </c>
+      <c r="E43" s="48">
         <f>MAX(0, E38 - E31)</f>
         <v>0</v>
       </c>
-      <c r="G43" s="52">
+      <c r="G43" s="60">
         <f>IF(E13*0.30 &lt;= E22, "⚠️ ALERTA: Suas despesas superam sua margem de crédito. Reduza seus custos ou aumente a renda para o banco aprovar.", IF(E43&lt;=0, HYPERLINK("https://wa.me/5511960364355?text=Olá,%20vi%20na%20minha%20simulação%20que%20tenho%20Perfil%20VIP!%20Quero%20fechar%20negócio.", "✅ PERFIL VIP: Entrada Coberta! Clique aqui para falar no WhatsApp!"), IF(TRIM(Z3)="Obra", "🏗️ PLANTA: Você precisará de R$ " &amp; TEXT(E45, "#,##0") &amp; " /mês para a entrada + R$ " &amp; TEXT(E46, "#,##0") &amp; " /mês (Evolução ao Banco).", "⏳ POUPANÇA: Guardando " &amp; TEXT(E44, "R$ #,##0") &amp; " /mês, em " &amp; IFERROR(INT(E43/MAX(1, E44)), 0) &amp; " meses você conquista seu lar!"))) </f>
         <v>0</v>
       </c>
-      <c r="H43" s="52"/>
-      <c r="I43" s="52"/>
-      <c r="J43" s="52"/>
-      <c r="K43" s="52"/>
+      <c r="H43" s="60"/>
+      <c r="I43" s="60"/>
+      <c r="J43" s="60"/>
+      <c r="K43" s="60"/>
     </row>
     <row r="44" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C44" s="8" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E44" s="18">
         <v>500</v>
       </c>
-      <c r="G44" s="52"/>
-      <c r="H44" s="52"/>
-      <c r="I44" s="52"/>
-      <c r="J44" s="52"/>
-      <c r="K44" s="52"/>
+      <c r="G44" s="60"/>
+      <c r="H44" s="60"/>
+      <c r="I44" s="60"/>
+      <c r="J44" s="60"/>
+      <c r="K44" s="60"/>
     </row>
     <row r="45" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C45" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="E45" s="40">
+        <v>175</v>
+      </c>
+      <c r="E45" s="48">
         <f>IF(E43&lt;=0, 0, IF(TRIM(Z3)="Obra", E43/MAX(1, Z4), E44))</f>
         <v>0</v>
       </c>
-      <c r="G45" s="52"/>
-      <c r="H45" s="52"/>
-      <c r="I45" s="52"/>
-      <c r="J45" s="52"/>
-      <c r="K45" s="52"/>
+      <c r="G45" s="60"/>
+      <c r="H45" s="60"/>
+      <c r="I45" s="60"/>
+      <c r="J45" s="60"/>
+      <c r="K45" s="60"/>
     </row>
     <row r="46" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C46" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="E46" s="40">
+        <v>176</v>
+      </c>
+      <c r="E46" s="48">
         <f>IF(TRIM(Z3)="Obra", E29 * 0.0002, 0)</f>
         <v>0</v>
       </c>
-      <c r="G46" s="52"/>
-      <c r="H46" s="52"/>
-      <c r="I46" s="52"/>
-      <c r="J46" s="52"/>
-      <c r="K46" s="52"/>
+      <c r="G46" s="60"/>
+      <c r="H46" s="60"/>
+      <c r="I46" s="60"/>
+      <c r="J46" s="60"/>
+      <c r="K46" s="60"/>
     </row>
     <row r="47" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="48" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1"/>
@@ -3512,1137 +3638,1137 @@
     <row r="5" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="6" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C6" s="6" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C7" s="5" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="D8" s="45">
+      <c r="D8" s="53">
         <f>"Plano Mensal para: " &amp; 'Início'!E23</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="C9" s="53" t="s">
-        <v>174</v>
-      </c>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53" t="s">
-        <v>175</v>
-      </c>
-      <c r="G9" s="53"/>
+      <c r="C9" s="61" t="s">
+        <v>179</v>
+      </c>
+      <c r="D9" s="61"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61" t="s">
+        <v>180</v>
+      </c>
+      <c r="G9" s="61"/>
     </row>
     <row r="10" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="C10" s="54">
+      <c r="C10" s="62">
         <f>SUMIF(B16:B200, "Sim", D16:D200) + SUMIF(B16:B200, "Sim", E16:E200)</f>
         <v>0</v>
       </c>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="55">
+      <c r="D10" s="62"/>
+      <c r="E10" s="62"/>
+      <c r="F10" s="63">
         <f>'Educação Financeira'!$Z$1 - (SUMIF(B16:B200, "Sim", D16:D200) + SUMIF(B16:B200, "Sim", E16:E200))</f>
         <v>0</v>
       </c>
-      <c r="G10" s="55"/>
+      <c r="G10" s="63"/>
     </row>
     <row r="11" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="55"/>
-      <c r="G11" s="55"/>
+      <c r="C11" s="62"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="63"/>
+      <c r="G11" s="63"/>
     </row>
     <row r="12" spans="2:12" ht="25" customHeight="1">
-      <c r="C12" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="D12" s="56"/>
-      <c r="E12" s="56"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="56"/>
+      <c r="C12" s="64" t="s">
+        <v>181</v>
+      </c>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="64"/>
     </row>
     <row r="13" spans="2:12" ht="25" customHeight="1">
-      <c r="C13" s="56"/>
-      <c r="D13" s="56"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="56"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="64"/>
     </row>
     <row r="14" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="C14" s="56"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="56"/>
-      <c r="F14" s="56"/>
-      <c r="G14" s="56"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
     </row>
     <row r="15" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B15" s="57" t="s">
-        <v>177</v>
-      </c>
-      <c r="C15" s="57" t="s">
-        <v>178</v>
-      </c>
-      <c r="D15" s="57" t="s">
-        <v>179</v>
-      </c>
-      <c r="E15" s="57" t="s">
-        <v>180</v>
-      </c>
-      <c r="F15" s="57" t="s">
-        <v>181</v>
-      </c>
-      <c r="G15" s="57" t="s">
+      <c r="B15" s="65" t="s">
         <v>182</v>
       </c>
-      <c r="H15" s="57" t="s">
+      <c r="C15" s="65" t="s">
         <v>183</v>
       </c>
+      <c r="D15" s="65" t="s">
+        <v>184</v>
+      </c>
+      <c r="E15" s="65" t="s">
+        <v>185</v>
+      </c>
+      <c r="F15" s="65" t="s">
+        <v>186</v>
+      </c>
+      <c r="G15" s="65" t="s">
+        <v>187</v>
+      </c>
+      <c r="H15" s="65" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="16" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B16" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C16" s="59">
+      <c r="B16" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C16" s="67">
         <f>EDATE(TODAY(), 0)</f>
         <v>0</v>
       </c>
-      <c r="D16" s="40">
+      <c r="D16" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E16" s="40">
+      <c r="E16" s="48">
         <f>IF(MONTH(C16)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="60">
+      <c r="F16" s="68">
         <f>'Educação Financeira'!$E$24 + IF(B16="Sim", D16 + E16, 0)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="61">
+      <c r="G16" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H16" s="62">
+      <c r="H16" s="70">
         <f>IF(F16&gt;=G16, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B17" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C17" s="59">
+      <c r="B17" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C17" s="67">
         <f>EDATE(TODAY(), 1)</f>
         <v>0</v>
       </c>
-      <c r="D17" s="40">
+      <c r="D17" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E17" s="40">
+      <c r="E17" s="48">
         <f>IF(MONTH(C17)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F17" s="60">
+      <c r="F17" s="68">
         <f>F16 + IF(B17="Sim", D17 + E17, 0)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="61">
+      <c r="G17" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H17" s="62">
+      <c r="H17" s="70">
         <f>IF(F17&gt;=G17, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B18" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C18" s="59">
+      <c r="B18" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C18" s="67">
         <f>EDATE(TODAY(), 2)</f>
         <v>0</v>
       </c>
-      <c r="D18" s="40">
+      <c r="D18" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E18" s="40">
+      <c r="E18" s="48">
         <f>IF(MONTH(C18)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F18" s="60">
+      <c r="F18" s="68">
         <f>F17 + IF(B18="Sim", D18 + E18, 0)</f>
         <v>0</v>
       </c>
-      <c r="G18" s="61">
+      <c r="G18" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H18" s="62">
+      <c r="H18" s="70">
         <f>IF(F18&gt;=G18, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B19" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C19" s="59">
+      <c r="B19" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C19" s="67">
         <f>EDATE(TODAY(), 3)</f>
         <v>0</v>
       </c>
-      <c r="D19" s="40">
+      <c r="D19" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E19" s="40">
+      <c r="E19" s="48">
         <f>IF(MONTH(C19)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F19" s="60">
+      <c r="F19" s="68">
         <f>F18 + IF(B19="Sim", D19 + E19, 0)</f>
         <v>0</v>
       </c>
-      <c r="G19" s="61">
+      <c r="G19" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H19" s="62">
+      <c r="H19" s="70">
         <f>IF(F19&gt;=G19, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B20" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C20" s="59">
+      <c r="B20" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C20" s="67">
         <f>EDATE(TODAY(), 4)</f>
         <v>0</v>
       </c>
-      <c r="D20" s="40">
+      <c r="D20" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E20" s="40">
+      <c r="E20" s="48">
         <f>IF(MONTH(C20)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F20" s="60">
+      <c r="F20" s="68">
         <f>F19 + IF(B20="Sim", D20 + E20, 0)</f>
         <v>0</v>
       </c>
-      <c r="G20" s="61">
+      <c r="G20" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H20" s="62">
+      <c r="H20" s="70">
         <f>IF(F20&gt;=G20, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B21" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C21" s="59">
+      <c r="B21" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C21" s="67">
         <f>EDATE(TODAY(), 5)</f>
         <v>0</v>
       </c>
-      <c r="D21" s="40">
+      <c r="D21" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E21" s="40">
+      <c r="E21" s="48">
         <f>IF(MONTH(C21)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F21" s="60">
+      <c r="F21" s="68">
         <f>F20 + IF(B21="Sim", D21 + E21, 0)</f>
         <v>0</v>
       </c>
-      <c r="G21" s="61">
+      <c r="G21" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H21" s="62">
+      <c r="H21" s="70">
         <f>IF(F21&gt;=G21, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B22" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C22" s="59">
+      <c r="B22" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C22" s="67">
         <f>EDATE(TODAY(), 6)</f>
         <v>0</v>
       </c>
-      <c r="D22" s="40">
+      <c r="D22" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E22" s="40">
+      <c r="E22" s="48">
         <f>IF(MONTH(C22)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F22" s="60">
+      <c r="F22" s="68">
         <f>F21 + IF(B22="Sim", D22 + E22, 0)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="61">
+      <c r="G22" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H22" s="62">
+      <c r="H22" s="70">
         <f>IF(F22&gt;=G22, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B23" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C23" s="59">
+      <c r="B23" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C23" s="67">
         <f>EDATE(TODAY(), 7)</f>
         <v>0</v>
       </c>
-      <c r="D23" s="40">
+      <c r="D23" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E23" s="40">
+      <c r="E23" s="48">
         <f>IF(MONTH(C23)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F23" s="60">
+      <c r="F23" s="68">
         <f>F22 + IF(B23="Sim", D23 + E23, 0)</f>
         <v>0</v>
       </c>
-      <c r="G23" s="61">
+      <c r="G23" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H23" s="62">
+      <c r="H23" s="70">
         <f>IF(F23&gt;=G23, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B24" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C24" s="59">
+      <c r="B24" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C24" s="67">
         <f>EDATE(TODAY(), 8)</f>
         <v>0</v>
       </c>
-      <c r="D24" s="40">
+      <c r="D24" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E24" s="40">
+      <c r="E24" s="48">
         <f>IF(MONTH(C24)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F24" s="60">
+      <c r="F24" s="68">
         <f>F23 + IF(B24="Sim", D24 + E24, 0)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="61">
+      <c r="G24" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H24" s="62">
+      <c r="H24" s="70">
         <f>IF(F24&gt;=G24, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B25" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C25" s="59">
+      <c r="B25" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C25" s="67">
         <f>EDATE(TODAY(), 9)</f>
         <v>0</v>
       </c>
-      <c r="D25" s="40">
+      <c r="D25" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E25" s="40">
+      <c r="E25" s="48">
         <f>IF(MONTH(C25)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F25" s="60">
+      <c r="F25" s="68">
         <f>F24 + IF(B25="Sim", D25 + E25, 0)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="61">
+      <c r="G25" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H25" s="62">
+      <c r="H25" s="70">
         <f>IF(F25&gt;=G25, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B26" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C26" s="59">
+      <c r="B26" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C26" s="67">
         <f>EDATE(TODAY(), 10)</f>
         <v>0</v>
       </c>
-      <c r="D26" s="40">
+      <c r="D26" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E26" s="40">
+      <c r="E26" s="48">
         <f>IF(MONTH(C26)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F26" s="60">
+      <c r="F26" s="68">
         <f>F25 + IF(B26="Sim", D26 + E26, 0)</f>
         <v>0</v>
       </c>
-      <c r="G26" s="61">
+      <c r="G26" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H26" s="62">
+      <c r="H26" s="70">
         <f>IF(F26&gt;=G26, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B27" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C27" s="59">
+      <c r="B27" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C27" s="67">
         <f>EDATE(TODAY(), 11)</f>
         <v>0</v>
       </c>
-      <c r="D27" s="40">
+      <c r="D27" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E27" s="40">
+      <c r="E27" s="48">
         <f>IF(MONTH(C27)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F27" s="60">
+      <c r="F27" s="68">
         <f>F26 + IF(B27="Sim", D27 + E27, 0)</f>
         <v>0</v>
       </c>
-      <c r="G27" s="61">
+      <c r="G27" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H27" s="62">
+      <c r="H27" s="70">
         <f>IF(F27&gt;=G27, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B28" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C28" s="59">
+      <c r="B28" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C28" s="67">
         <f>EDATE(TODAY(), 12)</f>
         <v>0</v>
       </c>
-      <c r="D28" s="40">
+      <c r="D28" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E28" s="40">
+      <c r="E28" s="48">
         <f>IF(MONTH(C28)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F28" s="60">
+      <c r="F28" s="68">
         <f>F27 + IF(B28="Sim", D28 + E28, 0)</f>
         <v>0</v>
       </c>
-      <c r="G28" s="61">
+      <c r="G28" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H28" s="62">
+      <c r="H28" s="70">
         <f>IF(F28&gt;=G28, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B29" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C29" s="59">
+      <c r="B29" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C29" s="67">
         <f>EDATE(TODAY(), 13)</f>
         <v>0</v>
       </c>
-      <c r="D29" s="40">
+      <c r="D29" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E29" s="40">
+      <c r="E29" s="48">
         <f>IF(MONTH(C29)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F29" s="60">
+      <c r="F29" s="68">
         <f>F28 + IF(B29="Sim", D29 + E29, 0)</f>
         <v>0</v>
       </c>
-      <c r="G29" s="61">
+      <c r="G29" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H29" s="62">
+      <c r="H29" s="70">
         <f>IF(F29&gt;=G29, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B30" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C30" s="59">
+      <c r="B30" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C30" s="67">
         <f>EDATE(TODAY(), 14)</f>
         <v>0</v>
       </c>
-      <c r="D30" s="40">
+      <c r="D30" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E30" s="40">
+      <c r="E30" s="48">
         <f>IF(MONTH(C30)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F30" s="60">
+      <c r="F30" s="68">
         <f>F29 + IF(B30="Sim", D30 + E30, 0)</f>
         <v>0</v>
       </c>
-      <c r="G30" s="61">
+      <c r="G30" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H30" s="62">
+      <c r="H30" s="70">
         <f>IF(F30&gt;=G30, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B31" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C31" s="59">
+      <c r="B31" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C31" s="67">
         <f>EDATE(TODAY(), 15)</f>
         <v>0</v>
       </c>
-      <c r="D31" s="40">
+      <c r="D31" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E31" s="40">
+      <c r="E31" s="48">
         <f>IF(MONTH(C31)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F31" s="60">
+      <c r="F31" s="68">
         <f>F30 + IF(B31="Sim", D31 + E31, 0)</f>
         <v>0</v>
       </c>
-      <c r="G31" s="61">
+      <c r="G31" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H31" s="62">
+      <c r="H31" s="70">
         <f>IF(F31&gt;=G31, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B32" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C32" s="59">
+      <c r="B32" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C32" s="67">
         <f>EDATE(TODAY(), 16)</f>
         <v>0</v>
       </c>
-      <c r="D32" s="40">
+      <c r="D32" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E32" s="40">
+      <c r="E32" s="48">
         <f>IF(MONTH(C32)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F32" s="60">
+      <c r="F32" s="68">
         <f>F31 + IF(B32="Sim", D32 + E32, 0)</f>
         <v>0</v>
       </c>
-      <c r="G32" s="61">
+      <c r="G32" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H32" s="62">
+      <c r="H32" s="70">
         <f>IF(F32&gt;=G32, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B33" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C33" s="59">
+      <c r="B33" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C33" s="67">
         <f>EDATE(TODAY(), 17)</f>
         <v>0</v>
       </c>
-      <c r="D33" s="40">
+      <c r="D33" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E33" s="40">
+      <c r="E33" s="48">
         <f>IF(MONTH(C33)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F33" s="60">
+      <c r="F33" s="68">
         <f>F32 + IF(B33="Sim", D33 + E33, 0)</f>
         <v>0</v>
       </c>
-      <c r="G33" s="61">
+      <c r="G33" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H33" s="62">
+      <c r="H33" s="70">
         <f>IF(F33&gt;=G33, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B34" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C34" s="59">
+      <c r="B34" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C34" s="67">
         <f>EDATE(TODAY(), 18)</f>
         <v>0</v>
       </c>
-      <c r="D34" s="40">
+      <c r="D34" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E34" s="40">
+      <c r="E34" s="48">
         <f>IF(MONTH(C34)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F34" s="60">
+      <c r="F34" s="68">
         <f>F33 + IF(B34="Sim", D34 + E34, 0)</f>
         <v>0</v>
       </c>
-      <c r="G34" s="61">
+      <c r="G34" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H34" s="62">
+      <c r="H34" s="70">
         <f>IF(F34&gt;=G34, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B35" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C35" s="59">
+      <c r="B35" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C35" s="67">
         <f>EDATE(TODAY(), 19)</f>
         <v>0</v>
       </c>
-      <c r="D35" s="40">
+      <c r="D35" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E35" s="40">
+      <c r="E35" s="48">
         <f>IF(MONTH(C35)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F35" s="60">
+      <c r="F35" s="68">
         <f>F34 + IF(B35="Sim", D35 + E35, 0)</f>
         <v>0</v>
       </c>
-      <c r="G35" s="61">
+      <c r="G35" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H35" s="62">
+      <c r="H35" s="70">
         <f>IF(F35&gt;=G35, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B36" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C36" s="59">
+      <c r="B36" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C36" s="67">
         <f>EDATE(TODAY(), 20)</f>
         <v>0</v>
       </c>
-      <c r="D36" s="40">
+      <c r="D36" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E36" s="40">
+      <c r="E36" s="48">
         <f>IF(MONTH(C36)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F36" s="60">
+      <c r="F36" s="68">
         <f>F35 + IF(B36="Sim", D36 + E36, 0)</f>
         <v>0</v>
       </c>
-      <c r="G36" s="61">
+      <c r="G36" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H36" s="62">
+      <c r="H36" s="70">
         <f>IF(F36&gt;=G36, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B37" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C37" s="59">
+      <c r="B37" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C37" s="67">
         <f>EDATE(TODAY(), 21)</f>
         <v>0</v>
       </c>
-      <c r="D37" s="40">
+      <c r="D37" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E37" s="40">
+      <c r="E37" s="48">
         <f>IF(MONTH(C37)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F37" s="60">
+      <c r="F37" s="68">
         <f>F36 + IF(B37="Sim", D37 + E37, 0)</f>
         <v>0</v>
       </c>
-      <c r="G37" s="61">
+      <c r="G37" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H37" s="62">
+      <c r="H37" s="70">
         <f>IF(F37&gt;=G37, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B38" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C38" s="59">
+      <c r="B38" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C38" s="67">
         <f>EDATE(TODAY(), 22)</f>
         <v>0</v>
       </c>
-      <c r="D38" s="40">
+      <c r="D38" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E38" s="40">
+      <c r="E38" s="48">
         <f>IF(MONTH(C38)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F38" s="60">
+      <c r="F38" s="68">
         <f>F37 + IF(B38="Sim", D38 + E38, 0)</f>
         <v>0</v>
       </c>
-      <c r="G38" s="61">
+      <c r="G38" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H38" s="62">
+      <c r="H38" s="70">
         <f>IF(F38&gt;=G38, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B39" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C39" s="59">
+      <c r="B39" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C39" s="67">
         <f>EDATE(TODAY(), 23)</f>
         <v>0</v>
       </c>
-      <c r="D39" s="40">
+      <c r="D39" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E39" s="40">
+      <c r="E39" s="48">
         <f>IF(MONTH(C39)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F39" s="60">
+      <c r="F39" s="68">
         <f>F38 + IF(B39="Sim", D39 + E39, 0)</f>
         <v>0</v>
       </c>
-      <c r="G39" s="61">
+      <c r="G39" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H39" s="62">
+      <c r="H39" s="70">
         <f>IF(F39&gt;=G39, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B40" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C40" s="59">
+      <c r="B40" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C40" s="67">
         <f>EDATE(TODAY(), 24)</f>
         <v>0</v>
       </c>
-      <c r="D40" s="40">
+      <c r="D40" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E40" s="40">
+      <c r="E40" s="48">
         <f>IF(MONTH(C40)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F40" s="60">
+      <c r="F40" s="68">
         <f>F39 + IF(B40="Sim", D40 + E40, 0)</f>
         <v>0</v>
       </c>
-      <c r="G40" s="61">
+      <c r="G40" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H40" s="62">
+      <c r="H40" s="70">
         <f>IF(F40&gt;=G40, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B41" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C41" s="59">
+      <c r="B41" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C41" s="67">
         <f>EDATE(TODAY(), 25)</f>
         <v>0</v>
       </c>
-      <c r="D41" s="40">
+      <c r="D41" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E41" s="40">
+      <c r="E41" s="48">
         <f>IF(MONTH(C41)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F41" s="60">
+      <c r="F41" s="68">
         <f>F40 + IF(B41="Sim", D41 + E41, 0)</f>
         <v>0</v>
       </c>
-      <c r="G41" s="61">
+      <c r="G41" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H41" s="62">
+      <c r="H41" s="70">
         <f>IF(F41&gt;=G41, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B42" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C42" s="59">
+      <c r="B42" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C42" s="67">
         <f>EDATE(TODAY(), 26)</f>
         <v>0</v>
       </c>
-      <c r="D42" s="40">
+      <c r="D42" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E42" s="40">
+      <c r="E42" s="48">
         <f>IF(MONTH(C42)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F42" s="60">
+      <c r="F42" s="68">
         <f>F41 + IF(B42="Sim", D42 + E42, 0)</f>
         <v>0</v>
       </c>
-      <c r="G42" s="61">
+      <c r="G42" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H42" s="62">
+      <c r="H42" s="70">
         <f>IF(F42&gt;=G42, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B43" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C43" s="59">
+      <c r="B43" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C43" s="67">
         <f>EDATE(TODAY(), 27)</f>
         <v>0</v>
       </c>
-      <c r="D43" s="40">
+      <c r="D43" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E43" s="40">
+      <c r="E43" s="48">
         <f>IF(MONTH(C43)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F43" s="60">
+      <c r="F43" s="68">
         <f>F42 + IF(B43="Sim", D43 + E43, 0)</f>
         <v>0</v>
       </c>
-      <c r="G43" s="61">
+      <c r="G43" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H43" s="62">
+      <c r="H43" s="70">
         <f>IF(F43&gt;=G43, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B44" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C44" s="59">
+      <c r="B44" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C44" s="67">
         <f>EDATE(TODAY(), 28)</f>
         <v>0</v>
       </c>
-      <c r="D44" s="40">
+      <c r="D44" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E44" s="40">
+      <c r="E44" s="48">
         <f>IF(MONTH(C44)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F44" s="60">
+      <c r="F44" s="68">
         <f>F43 + IF(B44="Sim", D44 + E44, 0)</f>
         <v>0</v>
       </c>
-      <c r="G44" s="61">
+      <c r="G44" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H44" s="62">
+      <c r="H44" s="70">
         <f>IF(F44&gt;=G44, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B45" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C45" s="59">
+      <c r="B45" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C45" s="67">
         <f>EDATE(TODAY(), 29)</f>
         <v>0</v>
       </c>
-      <c r="D45" s="40">
+      <c r="D45" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E45" s="40">
+      <c r="E45" s="48">
         <f>IF(MONTH(C45)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F45" s="60">
+      <c r="F45" s="68">
         <f>F44 + IF(B45="Sim", D45 + E45, 0)</f>
         <v>0</v>
       </c>
-      <c r="G45" s="61">
+      <c r="G45" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H45" s="62">
+      <c r="H45" s="70">
         <f>IF(F45&gt;=G45, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B46" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C46" s="59">
+      <c r="B46" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C46" s="67">
         <f>EDATE(TODAY(), 30)</f>
         <v>0</v>
       </c>
-      <c r="D46" s="40">
+      <c r="D46" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E46" s="40">
+      <c r="E46" s="48">
         <f>IF(MONTH(C46)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F46" s="60">
+      <c r="F46" s="68">
         <f>F45 + IF(B46="Sim", D46 + E46, 0)</f>
         <v>0</v>
       </c>
-      <c r="G46" s="61">
+      <c r="G46" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H46" s="62">
+      <c r="H46" s="70">
         <f>IF(F46&gt;=G46, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B47" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C47" s="59">
+      <c r="B47" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C47" s="67">
         <f>EDATE(TODAY(), 31)</f>
         <v>0</v>
       </c>
-      <c r="D47" s="40">
+      <c r="D47" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E47" s="40">
+      <c r="E47" s="48">
         <f>IF(MONTH(C47)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F47" s="60">
+      <c r="F47" s="68">
         <f>F46 + IF(B47="Sim", D47 + E47, 0)</f>
         <v>0</v>
       </c>
-      <c r="G47" s="61">
+      <c r="G47" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H47" s="62">
+      <c r="H47" s="70">
         <f>IF(F47&gt;=G47, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B48" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C48" s="59">
+      <c r="B48" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C48" s="67">
         <f>EDATE(TODAY(), 32)</f>
         <v>0</v>
       </c>
-      <c r="D48" s="40">
+      <c r="D48" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E48" s="40">
+      <c r="E48" s="48">
         <f>IF(MONTH(C48)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F48" s="60">
+      <c r="F48" s="68">
         <f>F47 + IF(B48="Sim", D48 + E48, 0)</f>
         <v>0</v>
       </c>
-      <c r="G48" s="61">
+      <c r="G48" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H48" s="62">
+      <c r="H48" s="70">
         <f>IF(F48&gt;=G48, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B49" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C49" s="59">
+      <c r="B49" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C49" s="67">
         <f>EDATE(TODAY(), 33)</f>
         <v>0</v>
       </c>
-      <c r="D49" s="40">
+      <c r="D49" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E49" s="40">
+      <c r="E49" s="48">
         <f>IF(MONTH(C49)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F49" s="60">
+      <c r="F49" s="68">
         <f>F48 + IF(B49="Sim", D49 + E49, 0)</f>
         <v>0</v>
       </c>
-      <c r="G49" s="61">
+      <c r="G49" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H49" s="62">
+      <c r="H49" s="70">
         <f>IF(F49&gt;=G49, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B50" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C50" s="59">
+      <c r="B50" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C50" s="67">
         <f>EDATE(TODAY(), 34)</f>
         <v>0</v>
       </c>
-      <c r="D50" s="40">
+      <c r="D50" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E50" s="40">
+      <c r="E50" s="48">
         <f>IF(MONTH(C50)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F50" s="60">
+      <c r="F50" s="68">
         <f>F49 + IF(B50="Sim", D50 + E50, 0)</f>
         <v>0</v>
       </c>
-      <c r="G50" s="61">
+      <c r="G50" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H50" s="62">
+      <c r="H50" s="70">
         <f>IF(F50&gt;=G50, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="B51" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="C51" s="59">
+      <c r="B51" s="66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C51" s="67">
         <f>EDATE(TODAY(), 35)</f>
         <v>0</v>
       </c>
-      <c r="D51" s="40">
+      <c r="D51" s="48">
         <f>'Educação Financeira'!$E$45</f>
         <v>0</v>
       </c>
-      <c r="E51" s="40">
+      <c r="E51" s="48">
         <f>IF(MONTH(C51)=12, 'Educação Financeira'!$E$13 * 0.5, 0)</f>
         <v>0</v>
       </c>
-      <c r="F51" s="60">
+      <c r="F51" s="68">
         <f>F50 + IF(B51="Sim", D51 + E51, 0)</f>
         <v>0</v>
       </c>
-      <c r="G51" s="61">
+      <c r="G51" s="69">
         <f>'Educação Financeira'!$Z$1</f>
         <v>0</v>
       </c>
-      <c r="H51" s="62">
+      <c r="H51" s="70">
         <f>IF(F51&gt;=G51, "✅ ATINGIDA", "⏳ EM CURSO")</f>
         <v>0</v>
       </c>
@@ -4979,7 +5105,7 @@
       <c r="B4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="40">
+      <c r="C4" s="48">
         <v>205000</v>
       </c>
       <c r="D4" t="s">
@@ -5008,7 +5134,7 @@
       <c r="B5" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="40">
+      <c r="C5" s="48">
         <v>226000</v>
       </c>
       <c r="D5" t="s">
@@ -5037,7 +5163,7 @@
       <c r="B6" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="40">
+      <c r="C6" s="48">
         <v>218000</v>
       </c>
       <c r="D6" t="s">
@@ -5066,7 +5192,7 @@
       <c r="B7" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="40">
+      <c r="C7" s="48">
         <v>214000</v>
       </c>
       <c r="D7" t="s">
@@ -5095,7 +5221,7 @@
       <c r="B8" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="40">
+      <c r="C8" s="48">
         <v>235000</v>
       </c>
       <c r="D8" t="s">
@@ -5124,7 +5250,7 @@
       <c r="B9" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="40">
+      <c r="C9" s="48">
         <v>217000</v>
       </c>
       <c r="D9" t="s">
@@ -5153,7 +5279,7 @@
       <c r="B10" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="40">
+      <c r="C10" s="48">
         <v>224000</v>
       </c>
       <c r="D10" t="s">
@@ -5182,7 +5308,7 @@
       <c r="B11" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="40">
+      <c r="C11" s="48">
         <v>218000</v>
       </c>
       <c r="D11" t="s">
@@ -5211,7 +5337,7 @@
       <c r="B12" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="40">
+      <c r="C12" s="48">
         <v>235000</v>
       </c>
       <c r="D12" t="s">
@@ -5240,7 +5366,7 @@
       <c r="B13" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="40">
+      <c r="C13" s="48">
         <v>235000</v>
       </c>
       <c r="D13" t="s">
@@ -5269,7 +5395,7 @@
       <c r="B14" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="40">
+      <c r="C14" s="48">
         <v>235000</v>
       </c>
       <c r="D14" t="s">
@@ -5298,7 +5424,7 @@
       <c r="B15" t="s">
         <v>49</v>
       </c>
-      <c r="C15" s="40">
+      <c r="C15" s="48">
         <v>244000</v>
       </c>
       <c r="D15" t="s">
@@ -5327,7 +5453,7 @@
       <c r="B16" t="s">
         <v>51</v>
       </c>
-      <c r="C16" s="40">
+      <c r="C16" s="48">
         <v>226000</v>
       </c>
       <c r="D16" t="s">
@@ -5356,7 +5482,7 @@
       <c r="B17" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="40">
+      <c r="C17" s="48">
         <v>306000</v>
       </c>
       <c r="D17" t="s">
@@ -5385,7 +5511,7 @@
       <c r="B18" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="40">
+      <c r="C18" s="48">
         <v>235000</v>
       </c>
       <c r="D18" t="s">
@@ -5414,7 +5540,7 @@
       <c r="B19" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="40">
+      <c r="C19" s="48">
         <v>239000</v>
       </c>
       <c r="D19" t="s">
@@ -5443,7 +5569,7 @@
       <c r="B20" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="40">
+      <c r="C20" s="48">
         <v>523000</v>
       </c>
       <c r="D20" t="s">
@@ -5472,7 +5598,7 @@
       <c r="B21" t="s">
         <v>69</v>
       </c>
-      <c r="C21" s="40">
+      <c r="C21" s="48">
         <v>209000</v>
       </c>
       <c r="D21" t="s">
@@ -5501,7 +5627,7 @@
       <c r="B22" t="s">
         <v>71</v>
       </c>
-      <c r="C22" s="40">
+      <c r="C22" s="48">
         <v>525000</v>
       </c>
       <c r="D22" t="s">
@@ -5530,7 +5656,7 @@
       <c r="B23" t="s">
         <v>75</v>
       </c>
-      <c r="C23" s="40">
+      <c r="C23" s="48">
         <v>537000</v>
       </c>
       <c r="D23" t="s">
@@ -5678,129 +5804,129 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="5" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="57" t="s">
-        <v>186</v>
-      </c>
-      <c r="B5" s="57" t="s">
-        <v>187</v>
-      </c>
-      <c r="C5" s="57" t="s">
-        <v>188</v>
-      </c>
-      <c r="D5" s="57" t="s">
-        <v>189</v>
-      </c>
-      <c r="E5" s="57" t="s">
-        <v>190</v>
+      <c r="A5" s="65" t="s">
+        <v>191</v>
+      </c>
+      <c r="B5" s="65" t="s">
+        <v>192</v>
+      </c>
+      <c r="C5" s="65" t="s">
+        <v>193</v>
+      </c>
+      <c r="D5" s="65" t="s">
+        <v>194</v>
+      </c>
+      <c r="E5" s="65" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="63" t="s">
+      <c r="A6" s="71" t="s">
         <v>109</v>
       </c>
-      <c r="B6" s="63" t="s">
-        <v>191</v>
-      </c>
-      <c r="C6" s="64" t="b">
-        <v>0</v>
-      </c>
-      <c r="D6" s="63"/>
-      <c r="E6" s="63"/>
+      <c r="B6" s="71" t="s">
+        <v>196</v>
+      </c>
+      <c r="C6" s="72" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" s="71"/>
+      <c r="E6" s="71"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="63" t="s">
+      <c r="A7" s="71" t="s">
         <v>110</v>
       </c>
-      <c r="B7" s="63" t="s">
-        <v>191</v>
-      </c>
-      <c r="C7" s="64" t="b">
-        <v>0</v>
-      </c>
-      <c r="D7" s="63"/>
-      <c r="E7" s="63"/>
+      <c r="B7" s="71" t="s">
+        <v>196</v>
+      </c>
+      <c r="C7" s="72" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" s="71"/>
+      <c r="E7" s="71"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="63" t="s">
-        <v>192</v>
-      </c>
-      <c r="B8" s="63" t="s">
-        <v>191</v>
-      </c>
-      <c r="C8" s="64" t="b">
-        <v>0</v>
-      </c>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
+      <c r="A8" s="71" t="s">
+        <v>197</v>
+      </c>
+      <c r="B8" s="71" t="s">
+        <v>196</v>
+      </c>
+      <c r="C8" s="72" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="71"/>
+      <c r="E8" s="71"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="63" t="s">
+      <c r="A9" s="71" t="s">
         <v>112</v>
       </c>
-      <c r="B9" s="63" t="s">
-        <v>191</v>
-      </c>
-      <c r="C9" s="64" t="b">
-        <v>0</v>
-      </c>
-      <c r="D9" s="63"/>
-      <c r="E9" s="63"/>
+      <c r="B9" s="71" t="s">
+        <v>196</v>
+      </c>
+      <c r="C9" s="72" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="63" t="s">
-        <v>193</v>
-      </c>
-      <c r="B10" s="63" t="s">
-        <v>191</v>
-      </c>
-      <c r="C10" s="64" t="b">
-        <v>0</v>
-      </c>
-      <c r="D10" s="63"/>
-      <c r="E10" s="63"/>
+      <c r="A10" s="71" t="s">
+        <v>198</v>
+      </c>
+      <c r="B10" s="71" t="s">
+        <v>196</v>
+      </c>
+      <c r="C10" s="72" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="63" t="s">
-        <v>194</v>
-      </c>
-      <c r="B11" s="63" t="s">
-        <v>191</v>
-      </c>
-      <c r="C11" s="64" t="b">
-        <v>0</v>
-      </c>
-      <c r="D11" s="63"/>
-      <c r="E11" s="63"/>
+      <c r="A11" s="71" t="s">
+        <v>199</v>
+      </c>
+      <c r="B11" s="71" t="s">
+        <v>196</v>
+      </c>
+      <c r="C11" s="72" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="63" t="s">
-        <v>195</v>
-      </c>
-      <c r="B12" s="63" t="s">
-        <v>196</v>
-      </c>
-      <c r="C12" s="64" t="b">
-        <v>0</v>
-      </c>
-      <c r="D12" s="63"/>
-      <c r="E12" s="63"/>
+      <c r="A12" s="71" t="s">
+        <v>200</v>
+      </c>
+      <c r="B12" s="71" t="s">
+        <v>201</v>
+      </c>
+      <c r="C12" s="72" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="71"/>
+      <c r="E12" s="71"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="63" t="s">
-        <v>197</v>
-      </c>
-      <c r="B13" s="63" t="s">
-        <v>198</v>
-      </c>
-      <c r="C13" s="64" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13" s="63"/>
-      <c r="E13" s="63"/>
+      <c r="A13" s="71" t="s">
+        <v>202</v>
+      </c>
+      <c r="B13" s="71" t="s">
+        <v>203</v>
+      </c>
+      <c r="C13" s="72" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" autoFilter="0"/>

--- a/Base_Template/template_mt_parceiros.xlsx
+++ b/Base_Template/template_mt_parceiros.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="202">
   <si>
     <t>PORTAL MT PARCEIROS</t>
   </si>
@@ -37,10 +37,10 @@
     <t>Nome</t>
   </si>
   <si>
-    <t>Preço</t>
-  </si>
-  <si>
-    <t>Área</t>
+    <t>Preco</t>
+  </si>
+  <si>
+    <t>Area</t>
   </si>
   <si>
     <t>Quartos</t>
@@ -320,9 +320,6 @@
     <t>Digite seu nome aqui...</t>
   </si>
   <si>
-    <t>INICIAR SIMULAÇÃO ▶</t>
-  </si>
-  <si>
     <t>⚠️ Valores estimados para fins de consultoria. MT Parceiros | (11) 96036-4355</t>
   </si>
   <si>
@@ -371,7 +368,7 @@
     <t>💬 Iniciar Atendimento</t>
   </si>
   <si>
-    <t>🤖 Simulação gerada por Algoritmo de IA MT Parceiros  •  Gerado em 03/03/2026 • © MT Parceiros</t>
+    <t>🤖 Simulação gerada por Algoritmo de IA MT Parceiros  •  Gerado em 04/03/2026 • © MT Parceiros</t>
   </si>
   <si>
     <t>📊 ANÁLISE EXECUTIVA (Algoritmo IA)</t>
@@ -417,9 +414,6 @@
   </si>
   <si>
     <t>TOTAL SUBSÍDIOS</t>
-  </si>
-  <si>
-    <t>SEU SCORE MT PARCEIROS</t>
   </si>
   <si>
     <t>JORNADA ATUAL:</t>
@@ -655,270 +649,270 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF1A1A2E"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="32"/>
       <color rgb="FFF35525"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="24"/>
       <color rgb="FF1A1A2E"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FF7A7A7A"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF1A1A2E"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF7A7A7A"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FF1A1A2E"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF1A1A2E"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="22"/>
       <color rgb="FFF35525"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="22"/>
       <color rgb="FF1A1A2E"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="22"/>
       <color rgb="FF27AE60"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FFF35525"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
       <color rgb="FF7A7A7A"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF7A7A7A"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFF35525"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF7A7A7A"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color rgb="FF1A1A2E"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color rgb="FFF35525"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FF1A1A2E"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FF2980B9"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FF27AE60"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="36"/>
       <color rgb="FFF35525"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFE74C3C"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFF35525"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF27AE60"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFF35525"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FFF35525"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF0000EE"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF7A7A7A"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FF27AE60"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Poppins"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1517,8 +1511,8 @@
   <tableColumns count="12">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Nome"/>
-    <tableColumn id="3" name="Preço" dataDxfId="0"/>
-    <tableColumn id="4" name="Área"/>
+    <tableColumn id="3" name="Preco" dataDxfId="0"/>
+    <tableColumn id="4" name="Area"/>
     <tableColumn id="5" name="Quartos"/>
     <tableColumn id="6" name="Bairro"/>
     <tableColumn id="7" name="Entrega"/>
@@ -1848,17 +1842,17 @@
     <row r="2" spans="2:12" ht="10" customHeight="1"/>
     <row r="3" spans="2:12" ht="45" customHeight="1">
       <c r="C3" s="1">
-        <f>HYPERLINK("#'Laudo de Crédito'!A1", "Laudo de Crédito")</f>
+        <f>HYPERLINK("#Laudo de Crédito.A1", "Laudo de Crédito")</f>
         <v>0</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1">
-        <f>HYPERLINK("#'Educação Financeira'!A1", "Educação Financeira")</f>
+        <f>HYPERLINK("#Educação Financeira.A1", "Educação Financeira")</f>
         <v>0</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1">
-        <f>HYPERLINK("#'Fluxo Mensal'!A1", "Fluxo Mensal")</f>
+        <f>HYPERLINK("#Fluxo Mensal.A1", "Fluxo Mensal")</f>
         <v>0</v>
       </c>
       <c r="H3" s="1"/>
@@ -2041,8 +2035,9 @@
     <row r="24" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="25" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="26" spans="3:11" ht="40" customHeight="1">
-      <c r="C26" s="10" t="s">
-        <v>99</v>
+      <c r="C26" s="10">
+        <f>HYPERLINK("#Laudo de Crédito.A1","INICIAR SIMULAÇÃO ▶")</f>
+        <v>0</v>
       </c>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
@@ -2067,7 +2062,7 @@
     <row r="28" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="29" spans="3:11">
       <c r="C29" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
@@ -2084,29 +2079,29 @@
     <row r="33" spans="3:26" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="34" spans="3:26" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C34" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="12"/>
       <c r="G34" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H34" s="13"/>
       <c r="I34" s="13"/>
       <c r="K34" s="14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L34" s="14"/>
     </row>
     <row r="35" spans="3:26" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C35" s="15">
-        <f>'Educação Financeira'!E33 * 0.5</f>
+        <f>'Educação Financeira'!E33*0.5</f>
         <v>0</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="15"/>
       <c r="G35" s="16">
-        <f>'Educação Financeira'!E33 / 2</f>
+        <f>'Educação Financeira'!E33/2</f>
         <v>0</v>
       </c>
       <c r="H35" s="16"/>
@@ -2122,17 +2117,17 @@
     </row>
     <row r="36" spans="3:26" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C36" s="19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D36" s="19"/>
       <c r="E36" s="19"/>
       <c r="G36" s="19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H36" s="19"/>
       <c r="I36" s="19"/>
       <c r="K36" s="19" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L36" s="19"/>
     </row>
@@ -2141,7 +2136,7 @@
     <row r="39" spans="3:26" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="40" spans="3:26" ht="30" customHeight="1">
       <c r="C40" s="20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D40" s="20"/>
       <c r="E40" s="20"/>
@@ -2154,7 +2149,7 @@
     </row>
     <row r="41" spans="3:26" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C41" s="21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D41" s="21"/>
       <c r="E41" s="21"/>
@@ -2168,17 +2163,17 @@
     <row r="42" spans="3:26" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="43" spans="3:26" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C43" s="22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D43" s="22"/>
       <c r="E43" s="22"/>
       <c r="G43" s="22" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H43" s="22"/>
       <c r="I43" s="22"/>
       <c r="K43" s="22" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L43" s="22"/>
     </row>
@@ -2195,17 +2190,17 @@
     <row r="45" spans="3:26" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="46" spans="3:26" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C46" s="22" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D46" s="22"/>
       <c r="E46" s="22"/>
       <c r="G46" s="22" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H46" s="22"/>
       <c r="I46" s="22"/>
       <c r="K46" s="22" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L46" s="22"/>
     </row>
@@ -2222,7 +2217,7 @@
     <row r="48" spans="3:26" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="49" spans="2:12" ht="40" customHeight="1">
       <c r="C49" s="23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D49" s="23"/>
       <c r="E49" s="23"/>
@@ -2256,7 +2251,7 @@
     <row r="60" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="61" spans="2:12" ht="30" customHeight="1">
       <c r="B61" s="24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C61" s="24"/>
       <c r="D61" s="24"/>
@@ -2396,7 +2391,6 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1"/>
-    <hyperlink ref="C26" location="'Laudo de Crédito'!A1" display="INICIAR SIMULAÇÃO ▶"/>
     <hyperlink ref="C49" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2439,17 +2433,17 @@
     <row r="2" spans="2:12" ht="10" customHeight="1"/>
     <row r="3" spans="2:12" ht="45" customHeight="1">
       <c r="C3" s="26">
-        <f>HYPERLINK("#'Laudo de Crédito'!A1", "Laudo de Crédito")</f>
+        <f>HYPERLINK("#Laudo de Crédito.A1", "Laudo de Crédito")</f>
         <v>0</v>
       </c>
       <c r="D3" s="26"/>
       <c r="E3" s="1">
-        <f>HYPERLINK("#'Educação Financeira'!A1", "Educação Financeira")</f>
+        <f>HYPERLINK("#Educação Financeira.A1", "Educação Financeira")</f>
         <v>0</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1">
-        <f>HYPERLINK("#'Fluxo Mensal'!A1", "Fluxo Mensal")</f>
+        <f>HYPERLINK("#Fluxo Mensal.A1", "Fluxo Mensal")</f>
         <v>0</v>
       </c>
       <c r="H3" s="1"/>
@@ -2472,17 +2466,17 @@
     <row r="5" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="6" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C6" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="2:12" ht="40" customHeight="1">
       <c r="C7" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C8" s="27" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D8" s="27"/>
       <c r="E8" s="27"/>
@@ -2496,13 +2490,13 @@
     <row r="9" spans="2:12" ht="20" customHeight="1"/>
     <row r="10" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C10" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="28">
-        <f>IF('Educação Financeira'!E33/'Educação Financeira'!E13 &lt;= 0.30, "Aprovação Provável", "Risco de Parcelamento")</f>
+        <f>IF('Educação Financeira'!E33/'Educação Financeira'!E13&lt;=0.30,"Aprovação Provável","Risco de Parcelamento")</f>
         <v>0</v>
       </c>
       <c r="H10" s="28"/>
@@ -2521,12 +2515,12 @@
     <row r="14" spans="2:12">
       <c r="B14" s="30"/>
       <c r="C14" s="31" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D14" s="31"/>
       <c r="F14" s="30"/>
       <c r="G14" s="31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H14" s="31"/>
     </row>
@@ -2547,12 +2541,12 @@
     <row r="18" spans="2:12">
       <c r="B18" s="30"/>
       <c r="C18" s="31" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D18" s="31"/>
       <c r="F18" s="30"/>
       <c r="G18" s="31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H18" s="31"/>
     </row>
@@ -2573,12 +2567,12 @@
     <row r="22" spans="2:12">
       <c r="B22" s="30"/>
       <c r="C22" s="31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D22" s="31"/>
       <c r="F22" s="30"/>
       <c r="G22" s="31" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H22" s="31"/>
     </row>
@@ -2598,26 +2592,26 @@
     <row r="25" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="26" spans="2:12" ht="25" customHeight="1">
       <c r="C26" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C27" s="35" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D27" s="35"/>
       <c r="E27" s="36" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F27" s="36"/>
       <c r="G27" s="36"/>
       <c r="H27" s="37" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I27" s="37"/>
       <c r="J27" s="37"/>
       <c r="K27" s="38" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L27" s="38"/>
     </row>
@@ -2647,13 +2641,8 @@
     </row>
     <row r="29" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="30" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="C30" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
       <c r="G30" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
@@ -2664,15 +2653,15 @@
       <c r="D31" s="43"/>
       <c r="E31" s="43"/>
       <c r="G31" s="44" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H31" s="44"/>
       <c r="I31" s="45" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="J31" s="45"/>
       <c r="K31" s="45" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L31" s="45"/>
     </row>
@@ -2691,10 +2680,10 @@
     <row r="34" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="35" spans="2:12" ht="25" customHeight="1">
       <c r="C35" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="36" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
@@ -2705,7 +2694,7 @@
     </row>
     <row r="37" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C37" s="47" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E37" s="48">
         <f>'Educação Financeira'!E29</f>
@@ -2716,17 +2705,17 @@
         <v>0</v>
       </c>
       <c r="I37" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="38" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="I38" s="47" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="39" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C39" s="47" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E39" s="48">
         <f>'Educação Financeira'!E30</f>
@@ -2744,7 +2733,7 @@
     <row r="40" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="41" spans="2:12" ht="30" customHeight="1">
       <c r="B41" s="24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C41" s="24"/>
       <c r="D41" s="24"/>
@@ -2868,7 +2857,7 @@
     <row r="150" s="3" customFormat="1" ht="20" customHeight="1"/>
   </sheetData>
   <sheetProtection sheet="1" autoFilter="0"/>
-  <mergeCells count="34">
+  <mergeCells count="33">
     <mergeCell ref="B1:L1"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="E3:F3"/>
@@ -2897,7 +2886,6 @@
     <mergeCell ref="H28:J28"/>
     <mergeCell ref="K27:L27"/>
     <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C30:E30"/>
     <mergeCell ref="C31:E32"/>
     <mergeCell ref="G31:H32"/>
     <mergeCell ref="I31:J32"/>
@@ -2952,22 +2940,22 @@
     <row r="2" spans="2:26" ht="10" customHeight="1"/>
     <row r="3" spans="2:26" ht="45" customHeight="1">
       <c r="C3" s="1">
-        <f>HYPERLINK("#'Laudo de Crédito'!A1", "Laudo de Crédito")</f>
+        <f>HYPERLINK("#Laudo de Crédito.A1", "Laudo de Crédito")</f>
         <v>0</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="26">
-        <f>HYPERLINK("#'Educação Financeira'!A1", "Educação Financeira")</f>
+        <f>HYPERLINK("#Educação Financeira.A1", "Educação Financeira")</f>
         <v>0</v>
       </c>
       <c r="F3" s="26"/>
       <c r="G3" s="1">
-        <f>HYPERLINK("#'Fluxo Mensal'!A1", "Fluxo Mensal")</f>
+        <f>HYPERLINK("#Fluxo Mensal.A1", "Fluxo Mensal")</f>
         <v>0</v>
       </c>
       <c r="H3" s="1"/>
       <c r="Z3" s="52">
-        <f>IFERROR(VLOOKUP(E36, Table_Empreendimentos[[Nome]:[Prazo_Meses]], 10, FALSE), "Pronto")</f>
+        <f>IFERROR(VLOOKUP(E36,'System Data'!B4:L200, 10, FALSE), "Pronto")</f>
         <v>0</v>
       </c>
     </row>
@@ -2986,14 +2974,14 @@
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="Z4" s="52">
-        <f>IFERROR(VLOOKUP(E36, Table_Empreendimentos[[Nome]:[Prazo_Meses]], 11, FALSE), 1)</f>
+        <f>IFERROR(VLOOKUP(E36,'System Data'!B4:L200, 11, FALSE), 1)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="2:26" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="6" spans="2:26" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C6" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
@@ -3006,12 +2994,12 @@
     </row>
     <row r="7" spans="2:26" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C7" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="2:26" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C8" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="2:26" s="3" customFormat="1" ht="20" customHeight="1">
@@ -3024,7 +3012,7 @@
     </row>
     <row r="10" spans="2:26" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C10" s="27" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D10" s="27"/>
       <c r="E10" s="27"/>
@@ -3048,12 +3036,12 @@
     </row>
     <row r="12" spans="2:26" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C12" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="2:26" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C13" s="8" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E13" s="18">
         <v>8000</v>
@@ -3065,7 +3053,7 @@
     </row>
     <row r="14" spans="2:26" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C14" s="8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E14" s="18">
         <v>15000</v>
@@ -3077,13 +3065,13 @@
     </row>
     <row r="15" spans="2:26" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C15" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="2:26" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="17" spans="3:7" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C17" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E17" s="18">
         <v>1200</v>
@@ -3095,7 +3083,7 @@
     </row>
     <row r="18" spans="3:7" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C18" s="8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E18" s="18">
         <v>800</v>
@@ -3107,7 +3095,7 @@
     </row>
     <row r="19" spans="3:7" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C19" s="8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E19" s="18">
         <v>400</v>
@@ -3119,7 +3107,7 @@
     </row>
     <row r="20" spans="3:7" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C20" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E20" s="18">
         <v>0</v>
@@ -3132,7 +3120,7 @@
     <row r="21" spans="3:7" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="22" spans="3:7" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C22" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E22" s="54">
         <f>SUM(E17:E21)</f>
@@ -3142,7 +3130,7 @@
     <row r="23" spans="3:7" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="24" spans="3:7" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C24" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E24" s="18">
         <v>30000</v>
@@ -3155,33 +3143,33 @@
     <row r="25" spans="3:7" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="26" spans="3:7" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C26" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E26" s="55" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="3:7" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="28" spans="3:7" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C28" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29" spans="3:7" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C29" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E29" s="48">
         <f>ROUND(MAX(0, (E13*0.30 - E22) * IF(E26="SIM", 142, 132)), 0)</f>
         <v>0</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="30" spans="3:7" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C30" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E30" s="48">
         <f>IF(E13&lt;=2850, 55000, IF(E13&lt;=4700, 35000, 0))</f>
@@ -3194,7 +3182,7 @@
     </row>
     <row r="31" spans="3:7" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C31" s="6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E31" s="56">
         <f>E29 + E30 + G30 + E24 + E14</f>
@@ -3204,7 +3192,7 @@
     <row r="32" spans="3:7" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="33" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C33" s="8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E33" s="48">
         <f>MAX(0, (E13 * 0.30) - E22)</f>
@@ -3214,40 +3202,40 @@
     <row r="34" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="35" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C35" s="6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="36" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C36" s="8" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E36" s="57" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F36" s="57"/>
     </row>
     <row r="37" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="38" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C38" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E38" s="56">
-        <f>IFERROR(VLOOKUP(E36, Table_Empreendimentos[[Nome]:[Prazo_Meses]], 2, FALSE), 0)</f>
+        <f>IFERROR(VLOOKUP(E36,'System Data'!B4:L200, 2, FALSE), 0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C39" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E39" s="58">
-        <f>IFERROR(VLOOKUP(E36, Table_Empreendimentos[[Nome]:[Prazo_Meses]], 5, FALSE), "---")</f>
+        <f>IFERROR(VLOOKUP(E36,'System Data'!B4:L200, 5, FALSE), "---")</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C40" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E40" s="59">
         <f>HYPERLINK("https://mtparceiros-alt.github.io/site-mt", "🔗 Abrir Imóvel")</f>
@@ -3257,12 +3245,12 @@
     <row r="41" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="42" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C42" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="43" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C43" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E43" s="48">
         <f>MAX(0, E38 - E31)</f>
@@ -3279,7 +3267,7 @@
     </row>
     <row r="44" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C44" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E44" s="18">
         <v>500</v>
@@ -3292,7 +3280,7 @@
     </row>
     <row r="45" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C45" s="8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E45" s="48">
         <f>IF(E43&lt;=0, 0, IF(TRIM(Z3)="Obra", E43/MAX(1, Z4), E44))</f>
@@ -3306,7 +3294,7 @@
     </row>
     <row r="46" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C46" s="8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E46" s="48">
         <f>IF(TRIM(Z3)="Obra", E29 * 0.0002, 0)</f>
@@ -3324,7 +3312,7 @@
     <row r="50" spans="2:26" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="51" spans="2:26" ht="30" customHeight="1">
       <c r="B51" s="24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C51" s="24"/>
       <c r="D51" s="24"/>
@@ -3605,17 +3593,17 @@
     <row r="2" spans="2:12" ht="10" customHeight="1"/>
     <row r="3" spans="2:12" ht="45" customHeight="1">
       <c r="C3" s="1">
-        <f>HYPERLINK("#'Laudo de Crédito'!A1", "Laudo de Crédito")</f>
+        <f>HYPERLINK("#Laudo de Crédito.A1", "Laudo de Crédito")</f>
         <v>0</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1">
-        <f>HYPERLINK("#'Educação Financeira'!A1", "Educação Financeira")</f>
+        <f>HYPERLINK("#Educação Financeira.A1", "Educação Financeira")</f>
         <v>0</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="26">
-        <f>HYPERLINK("#'Fluxo Mensal'!A1", "Fluxo Mensal")</f>
+        <f>HYPERLINK("#Fluxo Mensal.A1", "Fluxo Mensal")</f>
         <v>0</v>
       </c>
       <c r="H3" s="26"/>
@@ -3638,28 +3626,31 @@
     <row r="5" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="6" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C6" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C7" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="D8" s="53">
-        <f>"Plano Mensal para: " &amp; 'Início'!E23</f>
-        <v>0</v>
-      </c>
+        <f>'Início'!E23</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="53"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="53"/>
     </row>
     <row r="9" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="C9" s="61" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D9" s="61"/>
       <c r="E9" s="61"/>
       <c r="F9" s="61" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G9" s="61"/>
     </row>
@@ -3671,7 +3662,7 @@
       <c r="D10" s="62"/>
       <c r="E10" s="62"/>
       <c r="F10" s="63">
-        <f>'Educação Financeira'!$Z$1 - (SUMIF(B16:B200, "Sim", D16:D200) + SUMIF(B16:B200, "Sim", E16:E200))</f>
+        <f>'Educação Financeira'!$Z$1-(SUMIF(B16:B200,"Sim",D16:D200)+SUMIF(B16:B200,"Sim",E16:E200))</f>
         <v>0</v>
       </c>
       <c r="G10" s="63"/>
@@ -3685,7 +3676,7 @@
     </row>
     <row r="12" spans="2:12" ht="25" customHeight="1">
       <c r="C12" s="64" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D12" s="64"/>
       <c r="E12" s="64"/>
@@ -3708,30 +3699,30 @@
     </row>
     <row r="15" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B15" s="65" t="s">
+        <v>180</v>
+      </c>
+      <c r="C15" s="65" t="s">
+        <v>181</v>
+      </c>
+      <c r="D15" s="65" t="s">
         <v>182</v>
       </c>
-      <c r="C15" s="65" t="s">
+      <c r="E15" s="65" t="s">
         <v>183</v>
       </c>
-      <c r="D15" s="65" t="s">
+      <c r="F15" s="65" t="s">
         <v>184</v>
       </c>
-      <c r="E15" s="65" t="s">
+      <c r="G15" s="65" t="s">
         <v>185</v>
       </c>
-      <c r="F15" s="65" t="s">
+      <c r="H15" s="65" t="s">
         <v>186</v>
-      </c>
-      <c r="G15" s="65" t="s">
-        <v>187</v>
-      </c>
-      <c r="H15" s="65" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="16" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B16" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C16" s="67">
         <f>EDATE(TODAY(), 0)</f>
@@ -3760,7 +3751,7 @@
     </row>
     <row r="17" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B17" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C17" s="67">
         <f>EDATE(TODAY(), 1)</f>
@@ -3789,7 +3780,7 @@
     </row>
     <row r="18" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B18" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C18" s="67">
         <f>EDATE(TODAY(), 2)</f>
@@ -3818,7 +3809,7 @@
     </row>
     <row r="19" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B19" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C19" s="67">
         <f>EDATE(TODAY(), 3)</f>
@@ -3847,7 +3838,7 @@
     </row>
     <row r="20" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B20" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C20" s="67">
         <f>EDATE(TODAY(), 4)</f>
@@ -3876,7 +3867,7 @@
     </row>
     <row r="21" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B21" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C21" s="67">
         <f>EDATE(TODAY(), 5)</f>
@@ -3905,7 +3896,7 @@
     </row>
     <row r="22" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B22" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C22" s="67">
         <f>EDATE(TODAY(), 6)</f>
@@ -3934,7 +3925,7 @@
     </row>
     <row r="23" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B23" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C23" s="67">
         <f>EDATE(TODAY(), 7)</f>
@@ -3963,7 +3954,7 @@
     </row>
     <row r="24" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B24" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C24" s="67">
         <f>EDATE(TODAY(), 8)</f>
@@ -3992,7 +3983,7 @@
     </row>
     <row r="25" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B25" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C25" s="67">
         <f>EDATE(TODAY(), 9)</f>
@@ -4021,7 +4012,7 @@
     </row>
     <row r="26" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B26" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C26" s="67">
         <f>EDATE(TODAY(), 10)</f>
@@ -4050,7 +4041,7 @@
     </row>
     <row r="27" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B27" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C27" s="67">
         <f>EDATE(TODAY(), 11)</f>
@@ -4079,7 +4070,7 @@
     </row>
     <row r="28" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B28" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C28" s="67">
         <f>EDATE(TODAY(), 12)</f>
@@ -4108,7 +4099,7 @@
     </row>
     <row r="29" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B29" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C29" s="67">
         <f>EDATE(TODAY(), 13)</f>
@@ -4137,7 +4128,7 @@
     </row>
     <row r="30" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B30" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C30" s="67">
         <f>EDATE(TODAY(), 14)</f>
@@ -4166,7 +4157,7 @@
     </row>
     <row r="31" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B31" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C31" s="67">
         <f>EDATE(TODAY(), 15)</f>
@@ -4195,7 +4186,7 @@
     </row>
     <row r="32" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B32" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C32" s="67">
         <f>EDATE(TODAY(), 16)</f>
@@ -4224,7 +4215,7 @@
     </row>
     <row r="33" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B33" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C33" s="67">
         <f>EDATE(TODAY(), 17)</f>
@@ -4253,7 +4244,7 @@
     </row>
     <row r="34" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B34" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C34" s="67">
         <f>EDATE(TODAY(), 18)</f>
@@ -4282,7 +4273,7 @@
     </row>
     <row r="35" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B35" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C35" s="67">
         <f>EDATE(TODAY(), 19)</f>
@@ -4311,7 +4302,7 @@
     </row>
     <row r="36" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B36" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C36" s="67">
         <f>EDATE(TODAY(), 20)</f>
@@ -4340,7 +4331,7 @@
     </row>
     <row r="37" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B37" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C37" s="67">
         <f>EDATE(TODAY(), 21)</f>
@@ -4369,7 +4360,7 @@
     </row>
     <row r="38" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B38" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C38" s="67">
         <f>EDATE(TODAY(), 22)</f>
@@ -4398,7 +4389,7 @@
     </row>
     <row r="39" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B39" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C39" s="67">
         <f>EDATE(TODAY(), 23)</f>
@@ -4427,7 +4418,7 @@
     </row>
     <row r="40" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B40" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C40" s="67">
         <f>EDATE(TODAY(), 24)</f>
@@ -4456,7 +4447,7 @@
     </row>
     <row r="41" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B41" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C41" s="67">
         <f>EDATE(TODAY(), 25)</f>
@@ -4485,7 +4476,7 @@
     </row>
     <row r="42" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B42" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C42" s="67">
         <f>EDATE(TODAY(), 26)</f>
@@ -4514,7 +4505,7 @@
     </row>
     <row r="43" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B43" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C43" s="67">
         <f>EDATE(TODAY(), 27)</f>
@@ -4543,7 +4534,7 @@
     </row>
     <row r="44" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B44" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C44" s="67">
         <f>EDATE(TODAY(), 28)</f>
@@ -4572,7 +4563,7 @@
     </row>
     <row r="45" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B45" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C45" s="67">
         <f>EDATE(TODAY(), 29)</f>
@@ -4601,7 +4592,7 @@
     </row>
     <row r="46" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B46" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C46" s="67">
         <f>EDATE(TODAY(), 30)</f>
@@ -4630,7 +4621,7 @@
     </row>
     <row r="47" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B47" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C47" s="67">
         <f>EDATE(TODAY(), 31)</f>
@@ -4659,7 +4650,7 @@
     </row>
     <row r="48" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B48" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C48" s="67">
         <f>EDATE(TODAY(), 32)</f>
@@ -4688,7 +4679,7 @@
     </row>
     <row r="49" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B49" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C49" s="67">
         <f>EDATE(TODAY(), 33)</f>
@@ -4717,7 +4708,7 @@
     </row>
     <row r="50" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B50" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C50" s="67">
         <f>EDATE(TODAY(), 34)</f>
@@ -4746,7 +4737,7 @@
     </row>
     <row r="51" spans="2:8" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="B51" s="66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C51" s="67">
         <f>EDATE(TODAY(), 35)</f>
@@ -4789,7 +4780,7 @@
     <row r="65" spans="2:12" s="3" customFormat="1" ht="20" customHeight="1"/>
     <row r="66" spans="2:12" ht="30" customHeight="1">
       <c r="B66" s="24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C66" s="24"/>
       <c r="D66" s="24"/>
@@ -4888,12 +4879,13 @@
     <row r="150" s="3" customFormat="1" ht="20" customHeight="1"/>
   </sheetData>
   <sheetProtection sheet="1" autoFilter="0"/>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="B1:L1"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="B4:L4"/>
+    <mergeCell ref="D8:G8"/>
     <mergeCell ref="C9:E9"/>
     <mergeCell ref="C10:E11"/>
     <mergeCell ref="F9:G9"/>
@@ -5804,32 +5796,32 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="65" t="s">
+        <v>189</v>
+      </c>
+      <c r="B5" s="65" t="s">
+        <v>190</v>
+      </c>
+      <c r="C5" s="65" t="s">
         <v>191</v>
       </c>
-      <c r="B5" s="65" t="s">
+      <c r="D5" s="65" t="s">
         <v>192</v>
       </c>
-      <c r="C5" s="65" t="s">
+      <c r="E5" s="65" t="s">
         <v>193</v>
-      </c>
-      <c r="D5" s="65" t="s">
-        <v>194</v>
-      </c>
-      <c r="E5" s="65" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="71" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B6" s="71" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C6" s="72" t="b">
         <v>0</v>
@@ -5839,10 +5831,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="71" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B7" s="71" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C7" s="72" t="b">
         <v>0</v>
@@ -5852,10 +5844,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="71" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B8" s="71" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C8" s="72" t="b">
         <v>0</v>
@@ -5865,10 +5857,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="71" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B9" s="71" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C9" s="72" t="b">
         <v>0</v>
@@ -5878,10 +5870,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="71" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B10" s="71" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C10" s="72" t="b">
         <v>0</v>
@@ -5891,10 +5883,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="71" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B11" s="71" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C11" s="72" t="b">
         <v>0</v>
@@ -5904,10 +5896,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="71" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B12" s="71" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C12" s="72" t="b">
         <v>0</v>
@@ -5917,10 +5909,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="71" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B13" s="71" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C13" s="72" t="b">
         <v>0</v>
